--- a/ig/nr-fix-typo-practioner/ValueSet-fr-core-vs-title.xlsx
+++ b/ig/nr-fix-typo-practioner/ValueSet-fr-core-vs-title.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T12:47:09+00:00</t>
+    <t>2024-03-06T12:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
